--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -46,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -80,6 +94,27 @@
         <scheme val="minor"/>
       </rPr>
       <t>产品SKU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>启用时间</t>
     </r>
   </si>
 </sst>
@@ -709,7 +744,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -720,9 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1102,12 +1134,14 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
@@ -122,11 +122,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -744,11 +745,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1118,30 +1122,30 @@
     <col min="2" max="2" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.1416666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.1416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.8583333333333" customWidth="1"/>
+    <col min="5" max="5" width="27.8583333333333" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="35.25" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -116,6 +116,9 @@
       </rPr>
       <t>启用时间</t>
     </r>
+  </si>
+  <si>
+    <t>平台状态</t>
   </si>
 </sst>
 </file>
@@ -1115,17 +1118,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.1416666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.1416666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.8583333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:5">
+    <row r="1" ht="35.25" customHeight="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1141,6 +1145,9 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:3">
       <c r="A2" s="5"/>
@@ -1148,6 +1155,11 @@
       <c r="C2" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"在售,停售,草稿"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
@@ -1157,7 +1157,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
-      <formula1>"在售,停售,草稿"</formula1>
+      <formula1>"在售,停售,草稿,删除"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMappingCustomerTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -116,9 +116,6 @@
       </rPr>
       <t>启用时间</t>
     </r>
-  </si>
-  <si>
-    <t>平台状态</t>
   </si>
 </sst>
 </file>
@@ -1118,18 +1115,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="27.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.1416666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.1416666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.8583333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:6">
+    <row r="1" ht="35.25" customHeight="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1145,9 +1141,6 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:3">
       <c r="A2" s="5"/>
@@ -1155,11 +1148,6 @@
       <c r="C2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
-      <formula1>"在售,停售,草稿,删除"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
